--- a/data/availability/projects/madinet-masr/sarai.xlsx
+++ b/data/availability/projects/madinet-masr/sarai.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for sarai</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -554,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -754,7 +764,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S-Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1104,7 +1114,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Triplex</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1154,7 +1164,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1204,7 +1214,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1335,7 +1345,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1359,7 +1369,6 @@
       <c r="G2" t="n">
         <v>38</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1416,7 +1425,6 @@
       <c r="G3" t="n">
         <v>50</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1473,7 +1481,6 @@
       <c r="G4" t="n">
         <v>100</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1530,7 +1537,6 @@
       <c r="G5" t="n">
         <v>125</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1563,7 +1569,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S-Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1587,7 +1593,6 @@
       <c r="G6" t="n">
         <v>212</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1644,7 +1649,6 @@
       <c r="G7" t="n">
         <v>180</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1701,7 +1705,6 @@
       <c r="G8" t="n">
         <v>175</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1819,7 +1822,6 @@
       <c r="G10" t="n">
         <v>205</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1876,7 +1878,6 @@
       <c r="G11" t="n">
         <v>160</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1933,7 +1934,6 @@
       <c r="G12" t="n">
         <v>175</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Triplex</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1990,7 +1990,6 @@
       <c r="G13" t="n">
         <v>337</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2023,7 +2022,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2047,7 +2046,6 @@
       <c r="G14" t="n">
         <v>46</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2080,7 +2078,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2104,7 +2102,6 @@
       <c r="G15" t="n">
         <v>67</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
